--- a/data/MessageLimiter.xlsx
+++ b/data/MessageLimiter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,42 +460,41 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5"/>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="6">
+      <c r="A6" t="n">
         <v>68</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B6" t="n">
         <v>10</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C6" t="n">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D6" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/MessageLimiter.xlsx
+++ b/data/MessageLimiter.xlsx
@@ -424,17 +424,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>MaxRequests</t>
+          <t>max_requests</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>TimeWindow</t>
+          <t>time_window</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>TipMessage</t>
+          <t>tip_message</t>
         </is>
       </c>
     </row>
@@ -482,8 +482,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6">
       <c r="A6" t="n">
         <v>68</v>
